--- a/المنتجات/batch3-import-with-images-107.xlsx
+++ b/المنتجات/batch3-import-with-images-107.xlsx
@@ -825,6 +825,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Advanced Clinicals</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -1188,6 +1193,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Sunny Isle</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -3480,7 +3490,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>امبريوليس</t>
+          <t>إمبريوليس</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4030,6 +4040,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Mustela</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5957,6 +5972,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Neutrogena</t>
+        </is>
+      </c>
       <c r="V60" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6044,6 +6064,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Carefree</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6131,6 +6156,11 @@
           <t>g</t>
         </is>
       </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Carefree</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -9528,6 +9558,11 @@
       <c r="S99" t="inlineStr">
         <is>
           <t>g</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>L'Oréal Paris</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
